--- a/output/pdf_financials_xlsx/WAT.P.xlsx
+++ b/output/pdf_financials_xlsx/WAT.P.xlsx
@@ -3095,16 +3095,16 @@
         <v>0.125398</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.125398</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.125398</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.125398</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.125398</v>
       </c>
     </row>
     <row r="93">
@@ -4330,7 +4330,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -4498,7 +4502,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WAT.P.xlsx
+++ b/output/pdf_financials_xlsx/WAT.P.xlsx
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.372218</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.931817</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.810275</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.372218</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.931817</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.810275</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
